--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556077516</v>
+        <v>46157.93115050458</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93115050458</v>
+        <v>46157.9313847541</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9313847541</v>
+        <v>46157.93385346975</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93385346975</v>
+        <v>46157.93696722559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93696722559</v>
+        <v>46158.28205608267</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205608267</v>
+        <v>46158.29653966708</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29653966708</v>
+        <v>46158.29809146066</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29809146066</v>
+        <v>46158.33371634221</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33371634221</v>
+        <v>46158.37223276704</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Декабря/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37223276704</v>
+        <v>46158.37276248923</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
